--- a/Capítulo04/!Planilhas Resolvidas.xlsx
+++ b/Capítulo04/!Planilhas Resolvidas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Silvia\Documents\Livro Excel 2019\Avançado\Excel 2019\Planilhas\Capítulo4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuri.smendes\OneDrive - SENAC - SP\Capítulo04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DFE0A03-AD40-40E4-BF0F-288844AE5D99}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{537BAB8A-C0D7-4639-9045-7F950AF52712}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" activeTab="1" xr2:uid="{32F11FA9-375C-4E59-944C-2287961A96E5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{32F11FA9-375C-4E59-944C-2287961A96E5}"/>
   </bookViews>
   <sheets>
     <sheet name="ORIGINAL" sheetId="5" r:id="rId1"/>
@@ -26,7 +26,12 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -601,40 +606,12 @@
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="3">
     <dxf>
       <font>
         <b/>
         <i val="0"/>
         <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="3" tint="-0.24994659260841701"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="3" tint="-0.24994659260841701"/>
       </font>
     </dxf>
     <dxf>
@@ -665,9 +642,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -705,7 +682,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -811,7 +788,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -953,7 +930,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1718,11 +1695,11 @@
       </c>
       <c r="B2" s="11">
         <f ca="1">TODAY()</f>
-        <v>43535</v>
+        <v>46295</v>
       </c>
       <c r="C2" s="10" t="str">
         <f ca="1">VLOOKUP(WEEKDAY(B2,2),K16:L22,2)</f>
-        <v>segunda-feira</v>
+        <v>quarta-feira</v>
       </c>
       <c r="D2" s="12"/>
       <c r="E2" s="12"/>
@@ -1843,7 +1820,7 @@
       </c>
       <c r="I6" s="21" t="str">
         <f t="shared" ref="I6:I22" ca="1" si="5">IF(H6=$C$2,"Veículo no rodízio","Livre para circular")</f>
-        <v>Livre para circular</v>
+        <v>Veículo no rodízio</v>
       </c>
       <c r="K6" s="24" t="s">
         <v>34</v>
@@ -1885,7 +1862,7 @@
       </c>
       <c r="I7" s="21" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>Veículo no rodízio</v>
+        <v>Livre para circular</v>
       </c>
       <c r="K7" s="22" t="str">
         <f>"0"</f>
@@ -2014,7 +1991,7 @@
       </c>
       <c r="I10" s="21" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>Livre para circular</v>
+        <v>Veículo no rodízio</v>
       </c>
       <c r="K10" s="22" t="str">
         <f>"5"</f>
@@ -2100,7 +2077,7 @@
       </c>
       <c r="I12" s="21" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>Livre para circular</v>
+        <v>Veículo no rodízio</v>
       </c>
       <c r="K12" s="22" t="str">
         <f>"9"</f>
@@ -2143,7 +2120,7 @@
       </c>
       <c r="I13" s="21" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>Veículo no rodízio</v>
+        <v>Livre para circular</v>
       </c>
       <c r="K13" s="23"/>
       <c r="L13" s="23"/>
@@ -2522,23 +2499,7 @@
     <mergeCell ref="K5:L5"/>
     <mergeCell ref="K14:L14"/>
   </mergeCells>
-  <conditionalFormatting sqref="A2">
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
-      <formula>"Livre para circular"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
-      <formula>"Dia do rodízio"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C2">
-    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
-      <formula>"Livre para circular"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
-      <formula>"Dia do rodízio"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2">
+  <conditionalFormatting sqref="A2:C2">
     <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"Livre para circular"</formula>
     </cfRule>
@@ -2557,6 +2518,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100CEB2B541769F8A4991DE642272C524BB" ma:contentTypeVersion="0" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="7ae862ae5010eca0394e8ac9f072291e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="397561fba88d9dece65508bac662637b">
     <xsd:element name="properties">
@@ -2670,15 +2640,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -2686,13 +2647,34 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29AB35A9-25D2-4365-B112-9BF80396E583}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84FB20B5-DF85-4F05-A0D6-51BBBF1CAFB7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84FB20B5-DF85-4F05-A0D6-51BBBF1CAFB7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29AB35A9-25D2-4365-B112-9BF80396E583}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81DCE046-7CE9-4759-B28E-C2B429A2D199}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81DCE046-7CE9-4759-B28E-C2B429A2D199}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>